--- a/AAII_Financials/Quarterly/NRBO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NRBO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/NRBO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NRBO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>NRBO</t>
   </si>
@@ -656,122 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -847,8 +854,14 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -924,8 +937,14 @@
       <c r="AA9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1001,8 +1020,14 @@
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,85 +1055,93 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F12" s="3">
         <v>2300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>2400</v>
-      </c>
-      <c r="F12" s="3">
-        <v>600</v>
-      </c>
-      <c r="G12" s="3">
-        <v>300</v>
       </c>
       <c r="H12" s="3">
         <v>600</v>
       </c>
       <c r="I12" s="3">
+        <v>300</v>
+      </c>
+      <c r="J12" s="3">
+        <v>600</v>
+      </c>
+      <c r="K12" s="3">
         <v>1000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>900</v>
-      </c>
-      <c r="K12" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1400</v>
       </c>
       <c r="M12" s="3">
         <v>2000</v>
       </c>
       <c r="N12" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P12" s="3">
         <v>1100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>2200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>1100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>1800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>3500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>4000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>5000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,65 +1217,71 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>8200</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3">
         <v>17300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3">
         <v>13300</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1252,17 +1291,23 @@
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1338,8 +1383,14 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,85 +1415,93 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F17" s="3">
         <v>3900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>10400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>3100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>19500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>3100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>4700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>13800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>5900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>6500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>7100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1450,76 +1509,82 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="G18" s="3">
         <v>-3800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-10400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-4600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-3900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-19500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-2400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-4700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-13800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-2300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-2500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-3300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,8 +1612,10 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1556,26 +1623,26 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>400</v>
+      </c>
+      <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="G20" s="3">
         <v>3100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>5800</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1598,34 +1665,40 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>2700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-1100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-400</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-100</v>
       </c>
       <c r="Z20" s="3">
         <v>-200</v>
       </c>
       <c r="AA20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1633,65 +1706,65 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="G21" s="3">
         <v>-700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-2600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-4700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-3100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-3300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-4600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-3400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-3900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-3300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-19500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-2400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-4700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-11100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-3400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-1900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-2500</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1701,8 +1774,14 @@
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1778,85 +1857,97 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-2600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-4700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-3100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-3300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-4600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-3900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-19500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-4700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-11200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-3400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-1900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-2500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-3700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-6100</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-7200</v>
       </c>
       <c r="AA23" s="3">
         <v>-6700</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>-6700</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1932,8 +2023,14 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2106,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-4700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-3100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-3300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-4600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-3900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-19500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-4700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-11200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-3400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-2500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-3700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-6100</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-7200</v>
       </c>
       <c r="AA26" s="3">
         <v>-6700</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>-6700</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-4700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-3300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-3900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-19500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-4700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-11200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-3400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-3700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-6100</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-7200</v>
       </c>
       <c r="AA27" s="3">
         <v>-6700</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>-6700</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2355,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2438,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2521,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,8 +2604,14 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2480,26 +2619,26 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G32" s="3">
         <v>-3100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-5800</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2522,111 +2661,123 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-2700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>1100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>400</v>
-      </c>
-      <c r="X32" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>100</v>
       </c>
       <c r="Z32" s="3">
         <v>200</v>
       </c>
       <c r="AA32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-4700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-3300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-4600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-3900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-19500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-4700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-11200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-3400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-3700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-6100</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-7200</v>
       </c>
       <c r="AA33" s="3">
         <v>-6700</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>-6700</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2853,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-4700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-3300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-4600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-3900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-19500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-4700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-11200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-3400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-3700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-6100</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-7200</v>
       </c>
       <c r="AA35" s="3">
         <v>-6700</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>-6700</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +3059,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,85 +3090,93 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>22400</v>
+      </c>
+      <c r="F41" s="3">
         <v>25800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>28700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>30800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>33400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>11600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>16400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>9500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>13000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>10100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>12400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>14300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>9800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>13900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>5500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>19000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>23800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>28000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>34500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>18500</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3073,8 +3252,14 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3150,8 +3335,14 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3227,162 +3418,180 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>900</v>
-      </c>
-      <c r="M45" s="3">
-        <v>1000</v>
       </c>
       <c r="N45" s="3">
         <v>900</v>
       </c>
       <c r="O45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P45" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>22500</v>
+      </c>
+      <c r="F46" s="3">
         <v>26100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>29200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>31500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>33500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>7600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>10100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>13300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>16600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>10500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>13900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>10700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>12900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>15200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>11200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>14100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>6100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>19700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>24900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>28800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>34800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3458,20 +3667,26 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>200</v>
+      </c>
+      <c r="F48" s="3">
         <v>300</v>
       </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
       <c r="G48" s="3">
         <v>0</v>
       </c>
@@ -3482,19 +3697,19 @@
         <v>0</v>
       </c>
       <c r="J48" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3">
         <v>200</v>
       </c>
       <c r="M48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
@@ -3509,34 +3724,40 @@
         <v>300</v>
       </c>
       <c r="S48" s="3">
+        <v>300</v>
+      </c>
+      <c r="T48" s="3">
+        <v>300</v>
+      </c>
+      <c r="U48" s="3">
         <v>400</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
-      </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
       <c r="V48" s="3">
         <v>0</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>0</v>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3612,8 +3833,14 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3916,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,19 +3999,25 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
         <v>0</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>4</v>
@@ -3792,11 +4031,11 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -3804,29 +4043,29 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -3843,8 +4082,14 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,85 +4165,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>22800</v>
+      </c>
+      <c r="F54" s="3">
         <v>26400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>29200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>31500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>33500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>7600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>13500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>16800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>8100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>10700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>14200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>11000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>13200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>15600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>11500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>14500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>4000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>6200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>19700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>24900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>28800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>34800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4283,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,22 +4314,24 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>800</v>
+      </c>
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G57" s="3">
-        <v>700</v>
       </c>
       <c r="H57" s="3">
         <v>1100</v>
@@ -4079,61 +4340,67 @@
         <v>700</v>
       </c>
       <c r="J57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K57" s="3">
+        <v>700</v>
+      </c>
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>2000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>2400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>2800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4195,176 +4462,194 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>9400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>2700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>2400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F59" s="3">
         <v>2700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>9900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>11100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2500</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="R59" s="3">
-        <v>2400</v>
       </c>
       <c r="S59" s="3">
         <v>1400</v>
       </c>
       <c r="T59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="U59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V59" s="3">
         <v>400</v>
-      </c>
-      <c r="U59" s="3">
-        <v>400</v>
-      </c>
-      <c r="V59" s="3">
-        <v>500</v>
       </c>
       <c r="W59" s="3">
         <v>400</v>
       </c>
       <c r="X59" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z59" s="3">
         <v>1600</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>1100</v>
       </c>
       <c r="AA59" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC59" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F60" s="3">
         <v>4700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>11000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>11800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>3700</v>
-      </c>
-      <c r="S60" s="3">
-        <v>2100</v>
-      </c>
-      <c r="T60" s="3">
-        <v>3100</v>
       </c>
       <c r="U60" s="3">
         <v>2100</v>
       </c>
       <c r="V60" s="3">
+        <v>3100</v>
+      </c>
+      <c r="W60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="X60" s="3">
         <v>1700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>11900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>7600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>6200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>6300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4429,36 +4714,42 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>6400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>7500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>7800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>100</v>
+      </c>
+      <c r="F62" s="3">
         <v>200</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
@@ -4470,10 +4761,10 @@
         <v>0</v>
       </c>
       <c r="L62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
@@ -4494,10 +4785,10 @@
         <v>100</v>
       </c>
       <c r="T62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
@@ -4517,8 +4808,14 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4891,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4974,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,85 +5057,97 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F66" s="3">
         <v>4900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>11000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>11800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>3200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>3800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>2200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>11900</v>
-      </c>
-      <c r="X66" s="3">
-        <v>14000</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>13800</v>
       </c>
       <c r="Z66" s="3">
         <v>14000</v>
       </c>
       <c r="AA66" s="3">
+        <v>13800</v>
+      </c>
+      <c r="AB66" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AC66" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5175,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5254,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5337,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5420,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,85 +5503,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-115000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-108300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-103000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-99100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-98400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-95800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-91100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-88000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-84700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-81800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-77300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-73800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-69900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-66500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-47000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-44000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-41600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-36900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-94300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-90800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-87900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-84100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-80500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-74400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-67700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-60500</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5669,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5752,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,85 +5835,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F76" s="3">
         <v>21600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>25200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>20500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>21800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>11900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>14600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>6100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>9500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>13200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>7200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>9500</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>12300</v>
-      </c>
-      <c r="R76" s="3">
-        <v>7700</v>
       </c>
       <c r="S76" s="3">
         <v>12300</v>
       </c>
       <c r="T76" s="3">
+        <v>7700</v>
+      </c>
+      <c r="U76" s="3">
+        <v>12300</v>
+      </c>
+      <c r="V76" s="3">
         <v>-1000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>7800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>10900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>15000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>20800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +6001,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-4700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-3300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-4600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-3900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-19500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-4700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-11200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-3400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-3700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-6100</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-7200</v>
       </c>
       <c r="AA81" s="3">
         <v>-6700</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="AC81" s="3">
+        <v>-6700</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,8 +6207,10 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5874,23 +6271,29 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6369,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6452,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6535,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6618,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6701,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-2000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-4800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-6100</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-2000</v>
       </c>
       <c r="Q89" s="3">
         <v>-2300</v>
       </c>
       <c r="R89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="S89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="T89" s="3">
         <v>-4100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-3300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>3300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-6300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-7200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,8 +6819,10 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6412,17 +6853,17 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -6431,34 +6872,40 @@
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6981,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,8 +7064,14 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6638,58 +7097,64 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-600</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-6100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +7182,10 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6794,8 +7261,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7344,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7427,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,8 +7510,14 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7034,76 +7525,82 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>28800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>12900</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>9100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>6800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>24200</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>100</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>23200</v>
       </c>
       <c r="AA100" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>23200</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7113,11 +7610,11 @@
       <c r="E101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
@@ -7164,96 +7661,108 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>0</v>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-2100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>27000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-4800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>9400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-3500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>2900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-2300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>4500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-4100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-7200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-3500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>23000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-2500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>16000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-6900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NRBO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NRBO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
   <si>
     <t>NRBO</t>
   </si>
@@ -656,129 +656,133 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -860,8 +864,11 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -943,8 +950,11 @@
       <c r="AC9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1026,8 +1036,11 @@
       <c r="AC10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,91 +1070,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E12" s="3">
         <v>4900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>900</v>
-      </c>
-      <c r="X12" s="3">
-        <v>1800</v>
       </c>
       <c r="Y12" s="3">
         <v>1800</v>
       </c>
       <c r="Z12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AA12" s="3">
         <v>3500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>4000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>5000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,19 +1240,22 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
@@ -1243,23 +1263,23 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>8200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
@@ -1267,24 +1287,24 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3">
         <v>17300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="3">
         <v>13300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1297,8 +1317,8 @@
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1306,8 +1326,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,91 +1443,95 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E17" s="3">
         <v>6900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>19500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1509,82 +1539,85 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-5700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-19500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-13800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,8 +1647,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1623,29 +1657,29 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>200</v>
+      </c>
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5800</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1671,34 +1705,37 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>2700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-200</v>
       </c>
       <c r="AC20" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1706,68 +1743,68 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-5300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-19500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-11100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1780,8 +1817,11 @@
       <c r="AC21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1863,91 +1903,97 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-19500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2029,8 +2075,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-19500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-11200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-19500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-11200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,8 +2677,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2619,29 +2689,29 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5800</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2667,117 +2737,123 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-2700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>200</v>
       </c>
       <c r="AC32" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-19500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-11200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-19500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-11200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,91 +3178,95 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E41" s="3">
         <v>16000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>14300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>13900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>19000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>23800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>28000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>34500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>18500</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,8 +3348,11 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3341,8 +3434,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3424,174 +3520,183 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
         <v>800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1200</v>
       </c>
       <c r="K45" s="3">
         <v>1200</v>
       </c>
       <c r="L45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M45" s="3">
         <v>1700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1400</v>
-      </c>
-      <c r="U45" s="3">
-        <v>200</v>
       </c>
       <c r="V45" s="3">
         <v>200</v>
       </c>
       <c r="W45" s="3">
+        <v>200</v>
+      </c>
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E46" s="3">
         <v>16800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>26100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>29200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>31500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>33500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>11200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>14100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>19700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>24900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>28800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>34800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3673,8 +3778,11 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3685,11 +3793,11 @@
         <v>200</v>
       </c>
       <c r="F48" s="3">
+        <v>200</v>
+      </c>
+      <c r="G48" s="3">
         <v>300</v>
       </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
       <c r="H48" s="3">
         <v>0</v>
       </c>
@@ -3703,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="L48" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3">
         <v>200</v>
@@ -3712,7 +3820,7 @@
         <v>200</v>
       </c>
       <c r="O48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>300</v>
@@ -3730,25 +3838,25 @@
         <v>300</v>
       </c>
       <c r="U48" s="3">
+        <v>300</v>
+      </c>
+      <c r="V48" s="3">
         <v>400</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
       <c r="W48" s="3">
         <v>0</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>4</v>
+      <c r="Y48" s="3">
+        <v>0</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
+      <c r="AA48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB48" s="3">
         <v>0</v>
@@ -3756,8 +3864,11 @@
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,8 +4122,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4019,8 +4139,8 @@
       <c r="F52" s="3">
         <v>0</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
+      <c r="G52" s="3">
+        <v>0</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>4</v>
@@ -4037,8 +4157,8 @@
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -4049,17 +4169,17 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
+      <c r="T52" s="3">
+        <v>0</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>4</v>
@@ -4067,8 +4187,8 @@
       <c r="V52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E54" s="3">
         <v>17000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>26400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>31500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>33500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>11500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>19700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>24900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>28800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>34800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,91 +4446,95 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>700</v>
-      </c>
-      <c r="L57" s="3">
-        <v>800</v>
       </c>
       <c r="M57" s="3">
         <v>800</v>
       </c>
       <c r="N57" s="3">
+        <v>800</v>
+      </c>
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4468,188 +4602,197 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>9400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E59" s="3">
         <v>4700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1400</v>
-      </c>
-      <c r="V59" s="3">
-        <v>400</v>
       </c>
       <c r="W59" s="3">
         <v>400</v>
       </c>
       <c r="X59" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y59" s="3">
         <v>500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E60" s="3">
         <v>6800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4720,19 +4863,22 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>6400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4743,16 +4889,16 @@
         <v>100</v>
       </c>
       <c r="F62" s="3">
+        <v>100</v>
+      </c>
+      <c r="G62" s="3">
         <v>200</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
@@ -4767,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
@@ -4791,7 +4937,7 @@
         <v>100</v>
       </c>
       <c r="V62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5218,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E66" s="3">
         <v>6900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5680,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-125000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-115000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-108300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-103000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-99100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-98400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-95800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-91100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-88000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-84700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-81800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-77300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-73800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-69900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-66500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-47000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-44000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-41600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-36900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-94300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-90800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-87900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-84100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-80500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-74400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-67700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-60500</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6024,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E76" s="3">
         <v>10100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-1000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-19500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-11200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6277,14 +6476,14 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>4</v>
+      <c r="Y83" s="3">
+        <v>0</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3300</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-1200</v>
       </c>
       <c r="X89" s="3">
         <v>-1200</v>
       </c>
       <c r="Y89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Z89" s="3">
         <v>3300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7041,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6859,14 +7080,14 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -6878,13 +7099,13 @@
         <v>0</v>
       </c>
       <c r="U91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
+      <c r="W91" s="3">
+        <v>-100</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
@@ -6895,8 +7116,8 @@
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -6904,8 +7125,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,8 +7297,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7103,11 +7333,11 @@
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-600</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
@@ -7115,11 +7345,11 @@
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
@@ -7127,25 +7357,25 @@
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-6100</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
+      <c r="Y94" s="3">
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
@@ -7153,8 +7383,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,13 +7759,16 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>19200</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -7531,90 +7777,93 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>28800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>12900</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>9100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>6800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>24200</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>23200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>4</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
@@ -7667,14 +7916,14 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>4</v>
+      <c r="Y101" s="3">
+        <v>0</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
+      <c r="AA101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
@@ -7682,87 +7931,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>27000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-7200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>23000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>16000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-6900</v>
       </c>
     </row>
